--- a/public/file/Trax Agent Assign Template.xlsx
+++ b/public/file/Trax Agent Assign Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6EEC8F6-4CBB-4E65-8FED-A4C0346077A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D23D6965-E532-4299-9FAC-AE19A628C526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{395B0C63-56F6-410C-8B2D-73DC5C1DC16C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{968710E7-8F5A-4288-B76B-1C3A5F8D8615}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,10 @@
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -387,14 +390,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07CE767D-B3D7-4239-8AD9-1167FA550765}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70EEE581-8760-4245-9342-B83CEE7B79DC}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="26.5546875" customWidth="1"/>
-    <col min="2" max="2" width="31.44140625" customWidth="1"/>
-    <col min="3" max="3" width="19.21875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
